--- a/data/dividends_info_20260514.xlsx
+++ b/data/dividends_info_20260514.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>53.45000076293945</v>
+        <v>55.15999984741211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1683816627041157</v>
+        <v>0.1631617118364123</v>
       </c>
       <c r="J2" t="n">
         <v>305</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.75</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.212121212121212</v>
+        <v>1.204819308750574</v>
       </c>
       <c r="J3" t="n">
         <v>284</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.260000228881836</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6479481481313648</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J4" t="n">
         <v>214</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>53.45000076293945</v>
+        <v>55.15999984741211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1683816627041157</v>
+        <v>0.1631617118364123</v>
       </c>
       <c r="J6" t="n">
         <v>214</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.059999942779541</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.737864181496264</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>193</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.55500030517578</v>
+        <v>23.57999992370605</v>
       </c>
       <c r="I8" t="n">
-        <v>1.146253434523083</v>
+        <v>1.145038171643744</v>
       </c>
       <c r="J8" t="n">
         <v>193</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.800000190734863</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>3.44827574867131</v>
+        <v>3.430531777311974</v>
       </c>
       <c r="J9" t="n">
         <v>186</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.550000190734863</v>
+        <v>6.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9160305076764956</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="J10" t="n">
         <v>158</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.55500030517578</v>
+        <v>23.57999992370605</v>
       </c>
       <c r="I14" t="n">
-        <v>1.146253434523083</v>
+        <v>1.145038171643744</v>
       </c>
       <c r="J14" t="n">
         <v>130</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>53.45000076293945</v>
+        <v>55.15999984741211</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1683816627041157</v>
+        <v>0.1631617118364123</v>
       </c>
       <c r="J15" t="n">
         <v>130</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.860000133514404</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I18" t="n">
-        <v>4.266211506894081</v>
+        <v>4.280821805958635</v>
       </c>
       <c r="J18" t="n">
         <v>74</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.718999862670898</v>
+        <v>9.717000007629395</v>
       </c>
       <c r="I19" t="n">
-        <v>2.675172380633709</v>
+        <v>2.675722957660374</v>
       </c>
       <c r="J19" t="n">
         <v>67</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15.34000015258789</v>
+        <v>15.57999992370605</v>
       </c>
       <c r="I20" t="n">
-        <v>3.911342855487382</v>
+        <v>3.851091161348841</v>
       </c>
       <c r="J20" t="n">
         <v>67</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.75600004196167</v>
+        <v>3.706000089645386</v>
       </c>
       <c r="I21" t="n">
-        <v>5.857294929238052</v>
+        <v>5.936319338326055</v>
       </c>
       <c r="J21" t="n">
         <v>67</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.204999923706055</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="I23" t="n">
-        <v>1.611603565343367</v>
+        <v>1.618123022292755</v>
       </c>
       <c r="J23" t="n">
         <v>67</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>18.25</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="I24" t="n">
-        <v>2.06027397260274</v>
+        <v>2.06593397933063</v>
       </c>
       <c r="J24" t="n">
         <v>67</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.360000133514404</v>
+        <v>4.579999923706055</v>
       </c>
       <c r="I25" t="n">
-        <v>2.238805914381933</v>
+        <v>2.620087379890132</v>
       </c>
       <c r="J25" t="n">
         <v>60</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.239999771118164</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="I28" t="n">
-        <v>1.650943485346928</v>
+        <v>1.590909056427066</v>
       </c>
       <c r="J28" t="n">
         <v>53</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>33.75</v>
+        <v>34.45000076293945</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4354136333180191</v>
       </c>
       <c r="J29" t="n">
         <v>53</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.75</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7207206959519705</v>
       </c>
       <c r="J30" t="n">
         <v>46</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>23.70000076293945</v>
+        <v>23.10000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>1.054852286717788</v>
+        <v>1.08225106437896</v>
       </c>
       <c r="J31" t="n">
         <v>39</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>26.35000038146973</v>
+        <v>28.85000038146973</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7400379399505855</v>
+        <v>0.67590986974561</v>
       </c>
       <c r="J32" t="n">
         <v>39</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.835000038146973</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="I33" t="n">
-        <v>1.798365085230418</v>
+        <v>1.783783760795287</v>
       </c>
       <c r="J33" t="n">
         <v>39</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.894000053405762</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I34" t="n">
-        <v>5.925623147433098</v>
+        <v>5.942622811459178</v>
       </c>
       <c r="J34" t="n">
         <v>39</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.869999885559082</v>
+        <v>3.874000072479248</v>
       </c>
       <c r="I35" t="n">
-        <v>4.134367047323193</v>
+        <v>4.130098012559009</v>
       </c>
       <c r="J35" t="n">
         <v>39</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.73799991607666</v>
+        <v>2.691999912261963</v>
       </c>
       <c r="I36" t="n">
-        <v>5.062089271302936</v>
+        <v>5.148588577907525</v>
       </c>
       <c r="J36" t="n">
         <v>39</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.28000020980835</v>
+        <v>5.304999828338623</v>
       </c>
       <c r="I38" t="n">
-        <v>2.65151504615341</v>
+        <v>2.639019878042938</v>
       </c>
       <c r="J38" t="n">
         <v>39</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>19.10000038146973</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="I39" t="n">
-        <v>4.08376955194584</v>
+        <v>4.041450936962817</v>
       </c>
       <c r="J39" t="n">
         <v>39</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>24.31999969482422</v>
+        <v>24.3799991607666</v>
       </c>
       <c r="I40" t="n">
-        <v>3.495065833330981</v>
+        <v>3.486464435026964</v>
       </c>
       <c r="J40" t="n">
         <v>39</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>53.45000076293945</v>
+        <v>55.15999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1683816627041157</v>
+        <v>0.1631617118364123</v>
       </c>
       <c r="J41" t="n">
         <v>39</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.350000023841858</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7407407276587887</v>
+        <v>0.7518796749870864</v>
       </c>
       <c r="J42" t="n">
         <v>39</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.309999942779541</v>
+        <v>6.337999820709229</v>
       </c>
       <c r="I43" t="n">
-        <v>2.873217141744343</v>
+        <v>2.860523905469476</v>
       </c>
       <c r="J43" t="n">
         <v>39</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8.590000152587891</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I44" t="n">
-        <v>3.026775266373777</v>
+        <v>3.023255679851103</v>
       </c>
       <c r="J44" t="n">
         <v>39</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9.946000099182129</v>
+        <v>9.934000015258789</v>
       </c>
       <c r="I45" t="n">
-        <v>2.785039183970831</v>
+        <v>2.788403458571808</v>
       </c>
       <c r="J45" t="n">
         <v>39</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.195000052452087</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I46" t="n">
-        <v>1.129707063384524</v>
+        <v>1.163793136936023</v>
       </c>
       <c r="J46" t="n">
         <v>32</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.799999952316284</v>
+        <v>3.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.894736878429424</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="J47" t="n">
         <v>32</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.420000076293945</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="I48" t="n">
-        <v>0.991735505924209</v>
+        <v>1.00840331285605</v>
       </c>
       <c r="J48" t="n">
         <v>32</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.160000085830688</v>
+        <v>3.125</v>
       </c>
       <c r="I49" t="n">
-        <v>5.063291001713369</v>
+        <v>5.12</v>
       </c>
       <c r="J49" t="n">
         <v>25</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>27.39999961853027</v>
+        <v>27.25</v>
       </c>
       <c r="I51" t="n">
-        <v>4.051094946911317</v>
+        <v>4.073394495412844</v>
       </c>
       <c r="J51" t="n">
         <v>21</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9070000052452087</v>
+        <v>0.8880000114440918</v>
       </c>
       <c r="I52" t="n">
-        <v>3.307607478115665</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J52" t="n">
         <v>18</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.5070000290870667</v>
+        <v>0.5009999871253967</v>
       </c>
       <c r="I53" t="n">
-        <v>4.536488891611135</v>
+        <v>4.590818481247439</v>
       </c>
       <c r="J53" t="n">
         <v>18</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>20.20000076293945</v>
+        <v>20</v>
       </c>
       <c r="I54" t="n">
-        <v>2.970296917516995</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>18</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8.979999542236328</v>
+        <v>9</v>
       </c>
       <c r="I55" t="n">
-        <v>2.227171605736999</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="J55" t="n">
         <v>18</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.539999961853027</v>
+        <v>2.525000095367432</v>
       </c>
       <c r="I56" t="n">
-        <v>7.086614279658614</v>
+        <v>7.128712602040787</v>
       </c>
       <c r="J56" t="n">
         <v>11</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>14</v>
+        <v>14.38000011444092</v>
       </c>
       <c r="I58" t="n">
-        <v>1.785714285714286</v>
+        <v>1.738525716345029</v>
       </c>
       <c r="J58" t="n">
         <v>11</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.450000047683716</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8695652053727246</v>
+        <v>0.8720930087495459</v>
       </c>
       <c r="J59" t="n">
         <v>11</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>4.079999923706055</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="I60" t="n">
-        <v>3.676470656983444</v>
+        <v>3.640776800158699</v>
       </c>
       <c r="J60" t="n">
         <v>11</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13.94999980926514</v>
+        <v>13.75</v>
       </c>
       <c r="I61" t="n">
-        <v>4.157706150037241</v>
+        <v>4.218181818181818</v>
       </c>
       <c r="J61" t="n">
         <v>11</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2.358999967575073</v>
+        <v>2.336999893188477</v>
       </c>
       <c r="I62" t="n">
-        <v>4.408647792687614</v>
+        <v>4.450149968047624</v>
       </c>
       <c r="J62" t="n">
         <v>4</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10.66499996185303</v>
+        <v>10.88000011444092</v>
       </c>
       <c r="I63" t="n">
-        <v>2.719174880799652</v>
+        <v>2.665441148434234</v>
       </c>
       <c r="J63" t="n">
         <v>4</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.059999942779541</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I64" t="n">
-        <v>3.737864181496264</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J64" t="n">
         <v>4</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>39.13999938964844</v>
+        <v>39.18999862670898</v>
       </c>
       <c r="I65" t="n">
-        <v>4.190086932995046</v>
+        <v>4.184741151999679</v>
       </c>
       <c r="J65" t="n">
         <v>4</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>36.29999923706055</v>
+        <v>36.2400016784668</v>
       </c>
       <c r="I66" t="n">
-        <v>5.509641989077775</v>
+        <v>5.518763541306253</v>
       </c>
       <c r="J66" t="n">
         <v>4</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3.71399998664856</v>
+        <v>3.70199990272522</v>
       </c>
       <c r="I67" t="n">
-        <v>2.692514818510757</v>
+        <v>2.70124264256153</v>
       </c>
       <c r="J67" t="n">
         <v>4</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>29.67000007629395</v>
+        <v>29.6299991607666</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5003707435734662</v>
+        <v>0.5010462511135589</v>
       </c>
       <c r="J68" t="n">
         <v>4</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>20.68000030517578</v>
+        <v>21.05999946594238</v>
       </c>
       <c r="I69" t="n">
-        <v>4.448742680964772</v>
+        <v>4.368471145917155</v>
       </c>
       <c r="J69" t="n">
         <v>4</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>82.81999969482422</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="I71" t="n">
-        <v>1.255735334257667</v>
+        <v>1.251203038540282</v>
       </c>
       <c r="J71" t="n">
         <v>4</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>46.81000137329102</v>
+        <v>46.79000091552734</v>
       </c>
       <c r="I72" t="n">
-        <v>1.495406920452278</v>
+        <v>1.496046134437462</v>
       </c>
       <c r="J72" t="n">
         <v>4</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>57.75</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="I73" t="n">
-        <v>3.80952380952381</v>
+        <v>3.786574970358948</v>
       </c>
       <c r="J73" t="n">
         <v>4</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>9.527999877929688</v>
+        <v>9.465000152587891</v>
       </c>
       <c r="I74" t="n">
-        <v>9.026028663078311</v>
+        <v>9.086106562447984</v>
       </c>
       <c r="J74" t="n">
         <v>4</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>12.71599960327148</v>
+        <v>12.68000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>4.403900735070227</v>
+        <v>4.416403679197205</v>
       </c>
       <c r="J75" t="n">
         <v>4</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.190000057220459</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I76" t="n">
-        <v>1.826483970542351</v>
+        <v>1.843317907541938</v>
       </c>
       <c r="J76" t="n">
         <v>4</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.25</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="I77" t="n">
-        <v>3.243243243243243</v>
+        <v>3.232758713711175</v>
       </c>
       <c r="J77" t="n">
         <v>4</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.220000028610229</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I78" t="n">
-        <v>4.864864802168965</v>
+        <v>4.843049285931015</v>
       </c>
       <c r="J78" t="n">
         <v>4</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>88.40000152587891</v>
+        <v>96.80000305175781</v>
       </c>
       <c r="I79" t="n">
-        <v>2.33031670185768</v>
+        <v>2.128099106462365</v>
       </c>
       <c r="J79" t="n">
         <v>4</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>15.57999992370605</v>
+        <v>15.55000019073486</v>
       </c>
       <c r="I80" t="n">
-        <v>4.813863951686051</v>
+        <v>4.823151066241604</v>
       </c>
       <c r="J80" t="n">
         <v>4</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>14.78999996185303</v>
+        <v>14.57999992370605</v>
       </c>
       <c r="I81" t="n">
-        <v>2.028397571154647</v>
+        <v>2.057613179491319</v>
       </c>
       <c r="J81" t="n">
         <v>4</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>53.40000152587891</v>
+        <v>54</v>
       </c>
       <c r="I82" t="n">
-        <v>1.591760254141697</v>
+        <v>1.574074074074074</v>
       </c>
       <c r="J82" t="n">
         <v>4</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>36.91999816894531</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="I83" t="n">
-        <v>2.302275303780931</v>
+        <v>2.316076246130083</v>
       </c>
       <c r="J83" t="n">
         <v>4</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>70.68000030517578</v>
+        <v>69.45999908447266</v>
       </c>
       <c r="I84" t="n">
-        <v>1.839275600434318</v>
+        <v>1.871580790577072</v>
       </c>
       <c r="J84" t="n">
         <v>4</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>8</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="I85" t="n">
-        <v>7.5</v>
+        <v>7.575757502779743</v>
       </c>
       <c r="J85" t="n">
         <v>4</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>6.400000095367432</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I86" t="n">
-        <v>7.343749890569598</v>
+        <v>7.286821920907129</v>
       </c>
       <c r="J86" t="n">
         <v>4</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.800000190734863</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I87" t="n">
-        <v>3.44827574867131</v>
+        <v>3.430531777311974</v>
       </c>
       <c r="J87" t="n">
         <v>4</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>23.18000030517578</v>
+        <v>23.05999946594238</v>
       </c>
       <c r="I88" t="n">
-        <v>4.31406379134824</v>
+        <v>4.336513543623074</v>
       </c>
       <c r="J88" t="n">
         <v>4</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>4.699999809265137</v>
+        <v>4.860000133514404</v>
       </c>
       <c r="I89" t="n">
-        <v>4.574468270746932</v>
+        <v>4.423868191224254</v>
       </c>
       <c r="J89" t="n">
         <v>4</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.55500030517578</v>
+        <v>23.57999992370605</v>
       </c>
       <c r="I90" t="n">
-        <v>1.146253434523083</v>
+        <v>1.145038171643744</v>
       </c>
       <c r="J90" t="n">
         <v>4</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>8.239999771118164</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I91" t="n">
-        <v>2.427184533439133</v>
+        <v>2.227171605736999</v>
       </c>
       <c r="J91" t="n">
         <v>4</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>8.814999580383301</v>
+        <v>8.829999923706055</v>
       </c>
       <c r="I92" t="n">
-        <v>2.72263200708586</v>
+        <v>2.718006818501411</v>
       </c>
       <c r="J92" t="n">
         <v>4</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>21.60000038146973</v>
+        <v>21.6299991607666</v>
       </c>
       <c r="I93" t="n">
-        <v>3.65740734281527</v>
+        <v>3.652334862004688</v>
       </c>
       <c r="J93" t="n">
         <v>4</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5.260000228881836</v>
+        <v>5.320000171661377</v>
       </c>
       <c r="I94" t="n">
-        <v>1.768060759567112</v>
+        <v>1.748120244344976</v>
       </c>
       <c r="J94" t="n">
         <v>4</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>6.550000190734863</v>
+        <v>6.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9160305076764956</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="J95" t="n">
         <v>4</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>37.09999847412109</v>
+        <v>37.08000183105469</v>
       </c>
       <c r="I96" t="n">
-        <v>0.9433962652158614</v>
+        <v>0.9439050235075049</v>
       </c>
       <c r="J96" t="n">
         <v>4</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.15500020980835</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I97" t="n">
-        <v>7.747029821748212</v>
+        <v>7.698611315054664</v>
       </c>
       <c r="J97" t="n">
         <v>4</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2.269999980926514</v>
+        <v>2.25</v>
       </c>
       <c r="I98" t="n">
-        <v>2.643171828376432</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="J98" t="n">
         <v>4</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>7.135000228881836</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I100" t="n">
-        <v>1.443587900432929</v>
+        <v>1.446629236735053</v>
       </c>
       <c r="J100" t="n">
         <v>4</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5.782999992370605</v>
+        <v>5.826000213623047</v>
       </c>
       <c r="I101" t="n">
-        <v>3.285491963525215</v>
+        <v>3.261242585534401</v>
       </c>
       <c r="J101" t="n">
         <v>4</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>10.32499980926514</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="I102" t="n">
-        <v>4.184019447751901</v>
+        <v>4.169884308071058</v>
       </c>
       <c r="J102" t="n">
         <v>4</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>26.38999938964844</v>
+        <v>26.52000045776367</v>
       </c>
       <c r="I103" t="n">
-        <v>1.667298257583861</v>
+        <v>1.659125159898672</v>
       </c>
       <c r="J103" t="n">
         <v>4</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>2.941176525586755</v>
       </c>
       <c r="J104" t="n">
         <v>4</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>8.310000419616699</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="I105" t="n">
-        <v>5.655836056163266</v>
+        <v>5.548996283147359</v>
       </c>
       <c r="J105" t="n">
         <v>4</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>50.88000106811523</v>
+        <v>50.91999816894531</v>
       </c>
       <c r="I106" t="n">
-        <v>2.751572269280734</v>
+        <v>2.749410939401449</v>
       </c>
       <c r="J106" t="n">
         <v>4</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>3.79200005531311</v>
+        <v>3.796000003814697</v>
       </c>
       <c r="I107" t="n">
-        <v>7.911392289661467</v>
+        <v>7.903055840319345</v>
       </c>
       <c r="J107" t="n">
         <v>4</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>13.05000019073486</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="I108" t="n">
-        <v>0.919540216445335</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J108" t="n">
         <v>4</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.660000085830688</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I109" t="n">
-        <v>4.644808634243955</v>
+        <v>4.775280975630273</v>
       </c>
       <c r="J109" t="n">
         <v>4</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>22.04999923706055</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="I110" t="n">
-        <v>3.174603284445809</v>
+        <v>3.097345080462682</v>
       </c>
       <c r="J110" t="n">
         <v>4</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2.380000114440918</v>
+        <v>2.480000019073486</v>
       </c>
       <c r="I111" t="n">
-        <v>1.47058816458174</v>
+        <v>1.411290311726522</v>
       </c>
       <c r="J111" t="n">
         <v>4</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I112" t="n">
-        <v>5.670102925543355</v>
+        <v>5.660377432564756</v>
       </c>
       <c r="J112" t="n">
         <v>4</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.9879999756813049</v>
+        <v>0.9819999933242798</v>
       </c>
       <c r="I113" t="n">
-        <v>7.085020417306125</v>
+        <v>7.128309620760287</v>
       </c>
       <c r="J113" t="n">
         <v>4</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>51.65000152587891</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>1.374636939060416</v>
+        <v>1.370656390844167</v>
       </c>
       <c r="J114" t="n">
         <v>4</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>92</v>
+        <v>92.94999694824219</v>
       </c>
       <c r="I115" t="n">
-        <v>1.467391304347826</v>
+        <v>1.452393807771427</v>
       </c>
       <c r="J115" t="n">
         <v>4</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>7.039999961853027</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I116" t="n">
-        <v>1.136363642521141</v>
+        <v>1.126760578514967</v>
       </c>
       <c r="J116" t="n">
         <v>4</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>4.631999969482422</v>
+        <v>4.657999992370605</v>
       </c>
       <c r="I118" t="n">
-        <v>3.670120922280484</v>
+        <v>3.649635042474132</v>
       </c>
       <c r="J118" t="n">
         <v>4</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>59.5</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7563025210084033</v>
+        <v>0.7601351253389008</v>
       </c>
       <c r="J120" t="n">
         <v>4</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.21999979019165</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7662835557035801</v>
+        <v>0.7722007977909368</v>
       </c>
       <c r="J121" t="n">
         <v>4</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>39</v>
+        <v>39.2400016784668</v>
       </c>
       <c r="I122" t="n">
-        <v>2.692307692307693</v>
+        <v>2.67584086413583</v>
       </c>
       <c r="J122" t="n">
         <v>4</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>21.65999984741211</v>
+        <v>21.78000068664551</v>
       </c>
       <c r="I124" t="n">
-        <v>1.754385977271378</v>
+        <v>1.74471987153333</v>
       </c>
       <c r="J124" t="n">
         <v>4</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>27.1200008392334</v>
+        <v>26.94000053405762</v>
       </c>
       <c r="I125" t="n">
-        <v>2.212389312068178</v>
+        <v>2.227171448053531</v>
       </c>
       <c r="J125" t="n">
         <v>4</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>31.95000076293945</v>
+        <v>35.75</v>
       </c>
       <c r="I126" t="n">
-        <v>1.095461632683227</v>
+        <v>0.979020979020979</v>
       </c>
       <c r="J126" t="n">
         <v>4</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>3.700000047683716</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="I127" t="n">
-        <v>0.45945945353818</v>
+        <v>0.4696132745146338</v>
       </c>
       <c r="J127" t="n">
         <v>4</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.819999933242798</v>
+        <v>2.815000057220459</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3546099374726125</v>
+        <v>0.3552397796351747</v>
       </c>
       <c r="J128" t="n">
         <v>4</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>22.52000045776367</v>
+        <v>22.32999992370605</v>
       </c>
       <c r="I129" t="n">
-        <v>4.973356914892446</v>
+        <v>5.01567399832806</v>
       </c>
       <c r="J129" t="n">
         <v>4</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1.600000023841858</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I130" t="n">
-        <v>6.249999906867744</v>
+        <v>6.369426538796359</v>
       </c>
       <c r="J130" t="n">
         <v>4</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.736000061035156</v>
+        <v>2.716000080108643</v>
       </c>
       <c r="I131" t="n">
-        <v>9.502923764615339</v>
+        <v>9.572901043125144</v>
       </c>
       <c r="J131" t="n">
         <v>4</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.125999927520752</v>
+        <v>2.131999969482422</v>
       </c>
       <c r="I132" t="n">
-        <v>4.341486507369556</v>
+        <v>4.329268354652339</v>
       </c>
       <c r="J132" t="n">
         <v>4</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>8.680000305175781</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="I133" t="n">
-        <v>4.032257922747988</v>
+        <v>4.050925764956599</v>
       </c>
       <c r="J133" t="n">
         <v>-3</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>5.099999904632568</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I134" t="n">
-        <v>1.882352976375524</v>
+        <v>1.86407763538402</v>
       </c>
       <c r="J134" t="n">
         <v>-3</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>6.050000190734863</v>
+        <v>6</v>
       </c>
       <c r="I135" t="n">
-        <v>4.958677529621045</v>
+        <v>5</v>
       </c>
       <c r="J135" t="n">
         <v>-3</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>11.69999980926514</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I136" t="n">
-        <v>1.70940173726859</v>
+        <v>1.724137874335655</v>
       </c>
       <c r="J136" t="n">
         <v>-3</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>9.260000228881836</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6479481481313648</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J137" t="n">
         <v>-3</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>18.94000053405762</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I138" t="n">
-        <v>2.63991544826468</v>
+        <v>2.659574576015658</v>
       </c>
       <c r="J138" t="n">
         <v>-3</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>15.4399995803833</v>
+        <v>15.97999954223633</v>
       </c>
       <c r="I140" t="n">
-        <v>3.238342056921141</v>
+        <v>3.128911228554561</v>
       </c>
       <c r="J140" t="n">
         <v>-3</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>3.940000057220459</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="I141" t="n">
-        <v>2.538071029129546</v>
+        <v>2.617801092868345</v>
       </c>
       <c r="J141" t="n">
         <v>-3</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.579999923706055</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="I142" t="n">
-        <v>3.072625763805235</v>
+        <v>2.956989224569855</v>
       </c>
       <c r="J142" t="n">
         <v>-3</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1.220000028610229</v>
+        <v>1.200000047683716</v>
       </c>
       <c r="I145" t="n">
-        <v>2.459016335776212</v>
+        <v>2.49999990065893</v>
       </c>
       <c r="J145" t="n">
         <v>-3</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>8.300000190734863</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I147" t="n">
-        <v>1.204819249421562</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J147" t="n">
         <v>-3</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>7</v>
+        <v>7.019999980926514</v>
       </c>
       <c r="I148" t="n">
-        <v>3.142857142857143</v>
+        <v>3.133903142418014</v>
       </c>
       <c r="J148" t="n">
         <v>-3</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>27.5</v>
+        <v>28.10000038146973</v>
       </c>
       <c r="I149" t="n">
-        <v>2.218181818181818</v>
+        <v>2.170818475868273</v>
       </c>
       <c r="J149" t="n">
         <v>-10</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>10.75</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="I151" t="n">
-        <v>6.511627906976744</v>
+        <v>6.603773347250979</v>
       </c>
       <c r="J151" t="n">
         <v>-10</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>8.659999847412109</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I152" t="n">
-        <v>5.894919272458809</v>
+        <v>5.735955302032955</v>
       </c>
       <c r="J152" t="n">
         <v>-10</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8.399999618530273</v>
+        <v>8.314999580383301</v>
       </c>
       <c r="I153" t="n">
-        <v>3.214285860256279</v>
+        <v>3.24714388004279</v>
       </c>
       <c r="J153" t="n">
         <v>-10</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>6.804999828338623</v>
+        <v>7.59499979019165</v>
       </c>
       <c r="I154" t="n">
-        <v>5.143277131947396</v>
+        <v>4.608295058177587</v>
       </c>
       <c r="J154" t="n">
         <v>-10</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>17.70000076293945</v>
+        <v>17.60000038146973</v>
       </c>
       <c r="I156" t="n">
-        <v>4.237287952949482</v>
+        <v>4.261363544001069</v>
       </c>
       <c r="J156" t="n">
         <v>-10</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>10.64999961853027</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I157" t="n">
-        <v>4.037558830066335</v>
+        <v>4.075829310198792</v>
       </c>
       <c r="J157" t="n">
         <v>-10</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>4.085000038146973</v>
+        <v>4.09499979019165</v>
       </c>
       <c r="I158" t="n">
-        <v>3.671970589945027</v>
+        <v>3.663003850678582</v>
       </c>
       <c r="J158" t="n">
         <v>-10</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>11.77999973297119</v>
+        <v>12</v>
       </c>
       <c r="I159" t="n">
-        <v>1.673760649146206</v>
+        <v>1.643075</v>
       </c>
       <c r="J159" t="n">
         <v>-10</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>28.14999961853027</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="I160" t="n">
-        <v>3.907637708371066</v>
+        <v>3.978300235717942</v>
       </c>
       <c r="J160" t="n">
         <v>-10</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>64.09999847412109</v>
+        <v>67.80000305175781</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7332293466274444</v>
+        <v>0.6932153080306013</v>
       </c>
       <c r="J161" t="n">
         <v>-10</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>89.19999694824219</v>
+        <v>90.5</v>
       </c>
       <c r="I162" t="n">
-        <v>1.345291525846457</v>
+        <v>1.325966850828729</v>
       </c>
       <c r="J162" t="n">
         <v>-10</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>10.35000038146973</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I164" t="n">
-        <v>3.671497449220761</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J164" t="n">
         <v>-10</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>33.72499847412109</v>
+        <v>34.59999847412109</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8895478534423219</v>
+        <v>0.867052061358857</v>
       </c>
       <c r="J165" t="n">
         <v>-10</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>0.1712000072002411</v>
+        <v>0.1715999990701675</v>
       </c>
       <c r="I166" t="n">
-        <v>4.088784874764972</v>
+        <v>4.079254101357942</v>
       </c>
       <c r="J166" t="n">
         <v>-17</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.849999904632568</v>
+        <v>6.880000114440918</v>
       </c>
       <c r="I167" t="n">
-        <v>2.335766455876795</v>
+        <v>2.325581356665456</v>
       </c>
       <c r="J167" t="n">
         <v>-17</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>8.319999694824219</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I169" t="n">
-        <v>3.004807802523386</v>
+        <v>2.927400481460359</v>
       </c>
       <c r="J169" t="n">
         <v>-17</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>7.199999809265137</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I171" t="n">
-        <v>6.944444628409402</v>
+        <v>6.906077566391673</v>
       </c>
       <c r="J171" t="n">
         <v>-24</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>19.52499961853027</v>
+        <v>19.76000022888184</v>
       </c>
       <c r="I172" t="n">
-        <v>3.329065365937908</v>
+        <v>3.289473646108261</v>
       </c>
       <c r="J172" t="n">
         <v>-24</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>13.30500030517578</v>
+        <v>13.32999992370605</v>
       </c>
       <c r="I173" t="n">
-        <v>4.058624484134244</v>
+        <v>4.051012776374175</v>
       </c>
       <c r="J173" t="n">
         <v>-24</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>5.395999908447266</v>
+        <v>5.423999786376953</v>
       </c>
       <c r="I174" t="n">
-        <v>1.853224642266083</v>
+        <v>1.843657889721205</v>
       </c>
       <c r="J174" t="n">
         <v>-24</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>8.140000343322754</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="I175" t="n">
-        <v>1.965601882698298</v>
+        <v>1.96078435039117</v>
       </c>
       <c r="J175" t="n">
         <v>-24</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>286.5</v>
+        <v>287</v>
       </c>
       <c r="I176" t="n">
-        <v>1.261780104712042</v>
+        <v>1.259581881533101</v>
       </c>
       <c r="J176" t="n">
         <v>-24</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="I177" t="n">
-        <v>4.689655172413794</v>
+        <v>4.771929824561403</v>
       </c>
       <c r="J177" t="n">
         <v>-24</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>13.93000030517578</v>
+        <v>13.92500019073486</v>
       </c>
       <c r="I178" t="n">
-        <v>41.79181530840992</v>
+        <v>41.80682168947803</v>
       </c>
       <c r="J178" t="n">
         <v>-24</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>14.85000038146973</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="I179" t="n">
-        <v>3.939393838198014</v>
+        <v>3.950033649054687</v>
       </c>
       <c r="J179" t="n">
         <v>-24</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>20.92000007629395</v>
+        <v>20.77000045776367</v>
       </c>
       <c r="I180" t="n">
-        <v>3.011472264351955</v>
+        <v>3.033220924963969</v>
       </c>
       <c r="J180" t="n">
         <v>-24</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>154</v>
+        <v>156.3500061035156</v>
       </c>
       <c r="I181" t="n">
-        <v>0.5844155844155844</v>
+        <v>0.5756315733074749</v>
       </c>
       <c r="J181" t="n">
         <v>-24</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>72.08999633789062</v>
+        <v>72.34999847412109</v>
       </c>
       <c r="I182" t="n">
-        <v>2.387016350971216</v>
+        <v>2.378438198054025</v>
       </c>
       <c r="J182" t="n">
         <v>-24</v>
@@ -10678,7 +10678,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10688,14 +10688,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10739,14 +10739,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10763,7 +10763,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10773,14 +10773,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10790,14 +10790,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10814,7 +10814,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10824,14 +10824,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10848,7 +10848,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10858,14 +10858,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10882,7 +10882,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10892,14 +10892,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10909,14 +10909,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10926,14 +10926,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10960,14 +10960,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11011,14 +11011,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11052,7 +11052,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11062,14 +11062,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11086,7 +11086,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11096,14 +11096,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11147,14 +11147,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11171,7 +11171,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11188,7 +11188,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11205,7 +11205,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11222,7 +11222,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11273,7 +11273,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11334,14 +11334,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11358,7 +11358,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11375,7 +11375,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11392,7 +11392,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11402,14 +11402,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11426,7 +11426,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11443,7 +11443,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11460,7 +11460,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11470,14 +11470,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11487,14 +11487,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11528,7 +11528,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11538,14 +11538,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11562,7 +11562,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11572,14 +11572,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11589,14 +11589,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11613,7 +11613,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11630,7 +11630,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11647,7 +11647,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11664,7 +11664,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11674,14 +11674,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11698,7 +11698,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11708,14 +11708,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11725,14 +11725,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11749,7 +11749,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11783,7 +11783,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11793,14 +11793,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11810,14 +11810,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11827,14 +11827,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11868,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11885,7 +11885,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11919,7 +11919,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11953,7 +11953,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12048,14 +12048,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12072,7 +12072,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12089,7 +12089,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12099,14 +12099,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12123,7 +12123,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12140,7 +12140,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12191,7 +12191,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12201,14 +12201,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -12263,61 +12263,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Adventure S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>